--- a/deliverables/qc_gap_analysis/tracker/CoQ_Initial_List_2026-09-18.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Initial_List_2026-09-18.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -17281,7 +17281,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -19065,7 +19065,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
